--- a/assets/csv/faculty.xlsx
+++ b/assets/csv/faculty.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/hassan_491_osu_edu/Documents/Documents/GitHub/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44EEFF6-8BA7-FB45-962F-6A438EC996FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B44EEFF6-8BA7-FB45-962F-6A438EC996FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9260D48-F44D-8445-8266-0A50DAD788D1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t>Sl.</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>Electrical and Computer Engineering</t>
+  </si>
+  <si>
+    <t>Assistant Prof</t>
+  </si>
+  <si>
+    <t>ahmed.964</t>
   </si>
 </sst>
 </file>
@@ -920,8 +926,12 @@
       <c r="C15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="8"/>
+      <c r="D15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="F15" s="4" t="s">
         <v>61</v>
       </c>
